--- a/artfynd/A 28178-2023 artfynd.xlsx
+++ b/artfynd/A 28178-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28178-2023 artfynd.xlsx
+++ b/artfynd/A 28178-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113169341</v>
+        <v>113169338</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536308</v>
+        <v>536323</v>
       </c>
       <c r="R2" t="n">
-        <v>7022219</v>
+        <v>7022193</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113169338</v>
+        <v>113169349</v>
       </c>
       <c r="B3" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>5754</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536323</v>
+        <v>536360</v>
       </c>
       <c r="R3" t="n">
-        <v>7022193</v>
+        <v>7022033</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113169349</v>
+        <v>113169341</v>
       </c>
       <c r="B4" t="n">
-        <v>89878</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536360</v>
+        <v>536308</v>
       </c>
       <c r="R4" t="n">
-        <v>7022033</v>
+        <v>7022219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28178-2023 artfynd.xlsx
+++ b/artfynd/A 28178-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113169338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113169349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113169341</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>